--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83017A60-F156-4B8C-918D-6148D9015612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA189702-C781-495B-80BB-3ED2802E9D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BW$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BY$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -765,6 +765,30 @@
   </si>
   <si>
     <t>{adjustQty4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{restrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unRestrictedNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{unRestrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unRestrictedNetQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1203,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW7"/>
+  <dimension ref="A1:BY7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1221,16 +1245,16 @@
     <col min="18" max="19" width="5.4140625" customWidth="1"/>
     <col min="20" max="20" width="5.9140625" customWidth="1"/>
     <col min="21" max="22" width="5.75" customWidth="1"/>
-    <col min="23" max="33" width="6.33203125" customWidth="1"/>
-    <col min="34" max="34" width="8" customWidth="1"/>
-    <col min="35" max="39" width="7.08203125" customWidth="1"/>
-    <col min="40" max="74" width="6.08203125" customWidth="1"/>
-    <col min="75" max="75" width="8.4140625" customWidth="1"/>
-    <col min="76" max="79" width="6.08203125" customWidth="1"/>
-    <col min="80" max="81" width="16.75" customWidth="1"/>
+    <col min="23" max="35" width="6.33203125" customWidth="1"/>
+    <col min="36" max="36" width="8" customWidth="1"/>
+    <col min="37" max="41" width="7.08203125" customWidth="1"/>
+    <col min="42" max="76" width="6.08203125" customWidth="1"/>
+    <col min="77" max="77" width="8.4140625" customWidth="1"/>
+    <col min="78" max="81" width="6.08203125" customWidth="1"/>
+    <col min="82" max="83" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:77" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>140</v>
       </c>
@@ -1274,11 +1298,11 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AQ1" s="3"/>
-      <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3"/>
       <c r="AU1" s="3"/>
@@ -1301,21 +1325,23 @@
       <c r="BL1" s="3"/>
       <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
-      <c r="BO1" s="3" t="s">
+      <c r="BO1" s="3"/>
+      <c r="BP1" s="3"/>
+      <c r="BQ1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BP1" s="3"/>
-      <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
       <c r="BS1" s="3"/>
-      <c r="BT1" s="3" t="s">
+      <c r="BT1" s="3"/>
+      <c r="BU1" s="3"/>
+      <c r="BV1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BU1" s="3"/>
-      <c r="BV1" s="3"/>
       <c r="BW1" s="3"/>
+      <c r="BX1" s="3"/>
+      <c r="BY1" s="3"/>
     </row>
-    <row r="2" spans="1:75" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:77" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>126</v>
       </c>
@@ -1386,163 +1412,169 @@
         <v>82</v>
       </c>
       <c r="X2" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Z2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AA2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AB2" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AC2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AD2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AE2" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AF2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AG2" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AH2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AI2" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AK2" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AL2" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AM2" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AN2" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AO2" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AP2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AP2" s="12" t="s">
+      <c r="AR2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AQ2" s="12" t="s">
+      <c r="AS2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AR2" s="12" t="s">
+      <c r="AT2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AS2" s="12" t="s">
+      <c r="AU2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AT2" s="12" t="s">
+      <c r="AV2" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AW2" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="AX2" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AW2" s="12" t="s">
+      <c r="AY2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AX2" s="12" t="s">
+      <c r="AZ2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AY2" s="12" t="s">
+      <c r="BA2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AZ2" s="12" t="s">
+      <c r="BB2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="BA2" s="12" t="s">
+      <c r="BC2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="BB2" s="12" t="s">
+      <c r="BD2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="BC2" s="12" t="s">
+      <c r="BE2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="BD2" s="12" t="s">
+      <c r="BF2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="BE2" s="12" t="s">
+      <c r="BG2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="BF2" s="12" t="s">
+      <c r="BH2" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="BG2" s="12" t="s">
+      <c r="BI2" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="BH2" s="12" t="s">
+      <c r="BJ2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="BI2" s="12" t="s">
+      <c r="BK2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="BJ2" s="12" t="s">
+      <c r="BL2" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="BK2" s="12" t="s">
+      <c r="BM2" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BL2" s="12" t="s">
+      <c r="BN2" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="BM2" s="12" t="s">
+      <c r="BO2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BN2" s="12" t="s">
+      <c r="BP2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BO2" s="12" t="s">
+      <c r="BQ2" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="BP2" s="12" t="s">
+      <c r="BR2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="BQ2" s="12" t="s">
+      <c r="BS2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="BR2" s="12" t="s">
+      <c r="BT2" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="BU2" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="BT2" s="12" t="s">
+      <c r="BV2" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="BU2" s="12" t="s">
+      <c r="BW2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="BV2" s="12" t="s">
+      <c r="BX2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="BW2" s="12" t="s">
+      <c r="BY2" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:75" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:77" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>141</v>
       </c>
@@ -1613,163 +1645,169 @@
         <v>163</v>
       </c>
       <c r="X3" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y3" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AD3" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AE3" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AF3" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AG3" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AH3" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AI3" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AK3" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AJ3" s="7" t="s">
+      <c r="AL3" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AM3" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AN3" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AO3" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AP3" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AQ3" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AR3" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="AS3" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="AT3" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AU3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="AV3" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="AW3" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="AX3" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="AY3" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="AZ3" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="BA3" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="BB3" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="BA3" s="7" t="s">
+      <c r="BC3" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="BB3" s="7" t="s">
+      <c r="BD3" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="BC3" s="7" t="s">
+      <c r="BE3" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="BD3" s="7" t="s">
+      <c r="BF3" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="BE3" s="7" t="s">
+      <c r="BG3" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="BF3" s="7" t="s">
+      <c r="BH3" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="BG3" s="7" t="s">
+      <c r="BI3" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="BH3" s="7" t="s">
+      <c r="BJ3" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="BI3" s="7" t="s">
+      <c r="BK3" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="BJ3" s="7" t="s">
+      <c r="BL3" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="BK3" s="7" t="s">
+      <c r="BM3" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="BL3" s="7" t="s">
+      <c r="BN3" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="BM3" s="7" t="s">
+      <c r="BO3" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="BN3" s="7" t="s">
+      <c r="BP3" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="BO3" s="7" t="s">
+      <c r="BQ3" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="BP3" s="7" t="s">
+      <c r="BR3" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="BQ3" s="7" t="s">
+      <c r="BS3" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="BR3" s="7" t="s">
+      <c r="BT3" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="BS3" s="7" t="s">
+      <c r="BU3" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="BT3" s="7" t="s">
+      <c r="BV3" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="BU3" s="7" t="s">
+      <c r="BW3" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="BV3" s="7" t="s">
+      <c r="BX3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="BW3" s="7" t="s">
+      <c r="BY3" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:75" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:77" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>130</v>
       </c>
@@ -1840,174 +1878,180 @@
         <v>48</v>
       </c>
       <c r="X4" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Z4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AA4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="AA4" s="9" t="s">
+      <c r="AB4" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AC4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AC4" s="9" t="s">
+      <c r="AD4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AD4" s="9" t="s">
+      <c r="AE4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AE4" s="9" t="s">
+      <c r="AF4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AF4" s="9" t="s">
+      <c r="AG4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AG4" s="9" t="s">
+      <c r="AH4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AH4" s="9" t="s">
+      <c r="AI4" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AI4" s="9" t="s">
+      <c r="AK4" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="AJ4" s="9" t="s">
+      <c r="AL4" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="AK4" s="9" t="s">
+      <c r="AM4" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="AL4" s="9" t="s">
+      <c r="AN4" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="AM4" s="9" t="s">
+      <c r="AO4" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="AN4" s="9" t="s">
+      <c r="AP4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AO4" s="9" t="s">
+      <c r="AQ4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AP4" s="9" t="s">
+      <c r="AR4" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="AQ4" s="9" t="s">
+      <c r="AS4" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="AR4" s="9" t="s">
+      <c r="AT4" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="AS4" s="9" t="s">
+      <c r="AU4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="AT4" s="9" t="s">
+      <c r="AV4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="AU4" s="9" t="s">
+      <c r="AW4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="AV4" s="9" t="s">
+      <c r="AX4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AW4" s="9" t="s">
+      <c r="AY4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="AX4" s="9" t="s">
+      <c r="AZ4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AY4" s="9" t="s">
+      <c r="BA4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AZ4" s="9" t="s">
+      <c r="BB4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="BA4" s="9" t="s">
+      <c r="BC4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="BB4" s="9" t="s">
+      <c r="BD4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BC4" s="9" t="s">
+      <c r="BE4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BD4" s="9" t="s">
+      <c r="BF4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BE4" s="9" t="s">
+      <c r="BG4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BF4" s="9" t="s">
+      <c r="BH4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BG4" s="9" t="s">
+      <c r="BI4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="BH4" s="9" t="s">
+      <c r="BJ4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="BI4" s="9" t="s">
+      <c r="BK4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="BJ4" s="9" t="s">
+      <c r="BL4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="BK4" s="9" t="s">
+      <c r="BM4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="BL4" s="9" t="s">
+      <c r="BN4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="BM4" s="9" t="s">
+      <c r="BO4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BN4" s="9" t="s">
+      <c r="BP4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="BO4" s="9" t="s">
+      <c r="BQ4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="BP4" s="9" t="s">
+      <c r="BR4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="BQ4" s="9" t="s">
+      <c r="BS4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="BR4" s="9" t="s">
+      <c r="BT4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="BS4" s="9" t="s">
+      <c r="BU4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="BT4" s="9" t="s">
+      <c r="BV4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="BU4" s="9" t="s">
+      <c r="BW4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="BV4" s="9" t="s">
+      <c r="BX4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="BW4" s="11" t="s">
+      <c r="BY4" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:77" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>217</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BW4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BY4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA189702-C781-495B-80BB-3ED2802E9D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792ABDD7-6DAA-48F6-98A2-6F21CE3D8777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="70" yWindow="410" windowWidth="19200" windowHeight="9890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BY$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BR$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -52,12 +52,6 @@
     <t>{.mouldCavityQty}</t>
   </si>
   <si>
-    <t>{.heightQty}</t>
-  </si>
-  <si>
-    <t>{.cycleProductionQty}</t>
-  </si>
-  <si>
     <t>{.beginDay}</t>
   </si>
   <si>
@@ -154,26 +148,6 @@
     <t>{.day31}</t>
   </si>
   <si>
-    <t>{.conventionProductionQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.postponeProductionQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.midProductionQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.heightProductionQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.totalQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.prodReqPlan}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -214,14 +188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{.midQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.cycleReserveQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.totalAll}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -294,33 +260,6 @@
     <t>{.prodReqPlanA}</t>
   </si>
   <si>
-    <t>{.heightQtyA}</t>
-  </si>
-  <si>
-    <t>{.midQtyA}</t>
-  </si>
-  <si>
-    <t>{.cycleReserveQtyA}</t>
-  </si>
-  <si>
-    <t>{.totalQtyA}</t>
-  </si>
-  <si>
-    <t>{.heightProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.midProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.cycleProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.conventionProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.postponeProductionQtyA}</t>
-  </si>
-  <si>
     <t>{.beginDayA}</t>
   </si>
   <si>
@@ -467,18 +406,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{.actualOrderUnproducedA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.actualOrderUnproduced}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.differenceQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{factoryName}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -553,39 +480,6 @@
     <t>{prodReqPlan}</t>
   </si>
   <si>
-    <t>{heightQty}</t>
-  </si>
-  <si>
-    <t>{midQty}</t>
-  </si>
-  <si>
-    <t>{cycleReserveQty}</t>
-  </si>
-  <si>
-    <t>{totalQty}</t>
-  </si>
-  <si>
-    <t>{heightProductionQty}</t>
-  </si>
-  <si>
-    <t>{midProductionQty}</t>
-  </si>
-  <si>
-    <t>{cycleProductionQty}</t>
-  </si>
-  <si>
-    <t>{conventionProductionQty}</t>
-  </si>
-  <si>
-    <t>{postponeProductionQty}</t>
-  </si>
-  <si>
-    <t>{actualOrderUnproduced}</t>
-  </si>
-  <si>
-    <t>{differenceQty}</t>
-  </si>
-  <si>
     <t>{beginDay}</t>
   </si>
   <si>
@@ -702,30 +596,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{.conventionReserveQtyA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{conventionReserveQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.conventionReserveQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{specialMaterialResult}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.specialMaterialResult}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.differenceQtyA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.adjustQty1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -768,18 +638,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{.restrictedNetQtyA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{restrictedNetQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.restrictedNetQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.unRestrictedNetQtyA}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -789,6 +647,78 @@
   </si>
   <si>
     <t>{.unRestrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{productSurplus}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productSurplusA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productSurplus}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{adjustProductQty1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty1A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty2A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{adjustProductQty2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty3A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{adjustProductQty3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{adjustProductQty4}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.adjustProductQty4A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{originalTotalQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.originalTotalQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.originalTotalQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -912,7 +842,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -940,9 +870,6 @@
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1227,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BY7"/>
+  <dimension ref="A1:BR7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1245,18 +1172,17 @@
     <col min="18" max="19" width="5.4140625" customWidth="1"/>
     <col min="20" max="20" width="5.9140625" customWidth="1"/>
     <col min="21" max="22" width="5.75" customWidth="1"/>
-    <col min="23" max="35" width="6.33203125" customWidth="1"/>
-    <col min="36" max="36" width="8" customWidth="1"/>
-    <col min="37" max="41" width="7.08203125" customWidth="1"/>
-    <col min="42" max="76" width="6.08203125" customWidth="1"/>
-    <col min="77" max="77" width="8.4140625" customWidth="1"/>
-    <col min="78" max="81" width="6.08203125" customWidth="1"/>
-    <col min="82" max="83" width="16.75" customWidth="1"/>
+    <col min="23" max="26" width="6.33203125" customWidth="1"/>
+    <col min="27" max="34" width="7.08203125" customWidth="1"/>
+    <col min="35" max="69" width="6.08203125" customWidth="1"/>
+    <col min="70" max="70" width="8.4140625" customWidth="1"/>
+    <col min="71" max="74" width="6.08203125" customWidth="1"/>
+    <col min="75" max="76" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:70" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3"/>
@@ -1293,16 +1219,16 @@
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
-      <c r="AK1" s="3"/>
+      <c r="AK1" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3"/>
-      <c r="AR1" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3"/>
       <c r="AU1" s="3"/>
@@ -1320,496 +1246,447 @@
       <c r="BG1" s="3"/>
       <c r="BH1" s="3"/>
       <c r="BI1" s="3"/>
-      <c r="BJ1" s="3"/>
+      <c r="BJ1" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="BK1" s="3"/>
       <c r="BL1" s="3"/>
       <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
-      <c r="BO1" s="3"/>
+      <c r="BO1" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="BP1" s="3"/>
-      <c r="BQ1" s="3" t="s">
+      <c r="BQ1" s="3"/>
+      <c r="BR1" s="3"/>
+    </row>
+    <row r="2" spans="1:70" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ2" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK2" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL2" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR2" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT2" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW2" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX2" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AZ2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="BA2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="BB2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="BC2" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="BE2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="BF2" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="BG2" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH2" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="BI2" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ2" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="BK2" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="BL2" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="BM2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="BN2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="BO2" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP2" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="BQ2" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="BR2" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:70" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z3" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="BR1" s="3"/>
-      <c r="BS1" s="3"/>
-      <c r="BT1" s="3"/>
-      <c r="BU1" s="3"/>
-      <c r="BV1" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="BW1" s="3"/>
-      <c r="BX1" s="3"/>
-      <c r="BY1" s="3"/>
+      <c r="AA3" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH3" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI3" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AK3" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="AL3" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM3" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO3" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP3" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AS3" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AT3" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="AU3" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="AV3" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AW3" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="AX3" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AY3" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="AZ3" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA3" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="BB3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="BC3" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="BD3" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="BE3" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="BF3" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="BG3" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="BH3" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="BI3" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="BJ3" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="BK3" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="BL3" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM3" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="BN3" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="BO3" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="BP3" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="BQ3" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="BR3" s="7" t="s">
+        <v>178</v>
+      </c>
     </row>
-    <row r="2" spans="1:77" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA2" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB2" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="AC2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD2" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE2" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF2" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG2" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH2" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI2" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL2" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="AM2" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="AN2" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="AO2" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="AP2" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ2" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AR2" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS2" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="AT2" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU2" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="AV2" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW2" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="AX2" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="AY2" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AZ2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA2" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="BB2" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="BC2" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="BD2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="BE2" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="BF2" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="BG2" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="BH2" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="BI2" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="BJ2" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="BK2" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL2" s="12" t="s">
+    <row r="4" spans="1:70" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="BM2" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="BN2" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="BO2" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="BP2" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="BQ2" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR2" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="BS2" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="BT2" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU2" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV2" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW2" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX2" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="BY2" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:77" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF3" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="AH3" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI3" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ3" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="AK3" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL3" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="AM3" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="AN3" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="AO3" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="AP3" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="AQ3" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="AR3" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="AS3" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="AT3" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="AU3" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="AV3" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="AW3" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="AX3" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AY3" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="AZ3" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="BA3" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="BB3" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="BC3" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="BD3" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="BE3" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="BF3" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="BG3" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="BH3" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="BI3" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="BJ3" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="BK3" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="BL3" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="BM3" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="BN3" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="BO3" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="BP3" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="BQ3" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="BR3" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="BS3" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="BT3" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="BU3" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="BV3" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="BW3" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="BX3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="BY3" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:77" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>0</v>
@@ -1824,19 +1701,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>4</v>
@@ -1851,207 +1728,182 @@
         <v>7</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="R4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="T4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC4" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="AE4" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="AG4" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="AH4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AM4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AW4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AX4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="AZ4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="BB4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="BC4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="BD4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="BF4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="BG4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="BH4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="BI4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="BJ4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="BK4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="BL4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="BM4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="BO4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="BP4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="BQ4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="BR4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI4" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="AJ4" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="AK4" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="AL4" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="AO4" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="AP4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR4" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="AS4" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT4" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="AU4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="AV4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AW4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="AX4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="AZ4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="BA4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="BB4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="BC4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="BD4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="BE4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="BF4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="BH4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="BI4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="BJ4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="BK4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="BL4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="BM4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="BN4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="BO4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="BP4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="BQ4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="BR4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="BS4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="BT4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="BU4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="BV4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="BW4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="BX4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="BY4" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
-    <row r="6" spans="1:77" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>216</v>
-      </c>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:77" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>217</v>
-      </c>
+    <row r="7" spans="1:70" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BY4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BR4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792ABDD7-6DAA-48F6-98A2-6F21CE3D8777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0872739D-A532-4B92-ACA5-0EA8F1CE0AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="70" yWindow="410" windowWidth="19200" windowHeight="9890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BR$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BT$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -719,6 +719,30 @@
   </si>
   <si>
     <t>{.originalTotalQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{restrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.pendingQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{pendingQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.pendingQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1154,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BR7"/>
+  <dimension ref="A1:BT7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1172,15 +1196,15 @@
     <col min="18" max="19" width="5.4140625" customWidth="1"/>
     <col min="20" max="20" width="5.9140625" customWidth="1"/>
     <col min="21" max="22" width="5.75" customWidth="1"/>
-    <col min="23" max="26" width="6.33203125" customWidth="1"/>
-    <col min="27" max="34" width="7.08203125" customWidth="1"/>
-    <col min="35" max="69" width="6.08203125" customWidth="1"/>
-    <col min="70" max="70" width="8.4140625" customWidth="1"/>
-    <col min="71" max="74" width="6.08203125" customWidth="1"/>
-    <col min="75" max="76" width="16.75" customWidth="1"/>
+    <col min="23" max="28" width="6.33203125" customWidth="1"/>
+    <col min="29" max="36" width="7.08203125" customWidth="1"/>
+    <col min="37" max="71" width="6.08203125" customWidth="1"/>
+    <col min="72" max="72" width="8.4140625" customWidth="1"/>
+    <col min="73" max="76" width="6.08203125" customWidth="1"/>
+    <col min="77" max="78" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:72" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>119</v>
       </c>
@@ -1219,11 +1243,11 @@
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
@@ -1246,21 +1270,23 @@
       <c r="BG1" s="3"/>
       <c r="BH1" s="3"/>
       <c r="BI1" s="3"/>
-      <c r="BJ1" s="3" t="s">
+      <c r="BJ1" s="3"/>
+      <c r="BK1" s="3"/>
+      <c r="BL1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="BK1" s="3"/>
-      <c r="BL1" s="3"/>
       <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
-      <c r="BO1" s="3" t="s">
+      <c r="BO1" s="3"/>
+      <c r="BP1" s="3"/>
+      <c r="BQ1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="BP1" s="3"/>
-      <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
+      <c r="BS1" s="3"/>
+      <c r="BT1" s="3"/>
     </row>
-    <row r="2" spans="1:70" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:72" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>108</v>
       </c>
@@ -1334,145 +1360,151 @@
         <v>193</v>
       </c>
       <c r="Y2" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z2" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="AA2" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB2" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AC2" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AD2" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AE2" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AF2" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AG2" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AH2" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="AG2" s="11" t="s">
+      <c r="AI2" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="AH2" s="11" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="AI2" s="11" t="s">
+      <c r="AK2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AJ2" s="11" t="s">
+      <c r="AL2" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AK2" s="11" t="s">
+      <c r="AM2" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="AL2" s="11" t="s">
+      <c r="AN2" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="AM2" s="11" t="s">
+      <c r="AO2" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AN2" s="11" t="s">
+      <c r="AP2" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AO2" s="11" t="s">
+      <c r="AQ2" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AP2" s="11" t="s">
+      <c r="AR2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AQ2" s="11" t="s">
+      <c r="AS2" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="AR2" s="11" t="s">
+      <c r="AT2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AS2" s="11" t="s">
+      <c r="AU2" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AT2" s="11" t="s">
+      <c r="AV2" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AU2" s="11" t="s">
+      <c r="AW2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="AV2" s="11" t="s">
+      <c r="AX2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="AW2" s="11" t="s">
+      <c r="AY2" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="AX2" s="11" t="s">
+      <c r="AZ2" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="AY2" s="11" t="s">
+      <c r="BA2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="AZ2" s="11" t="s">
+      <c r="BB2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="BA2" s="11" t="s">
+      <c r="BC2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="BB2" s="11" t="s">
+      <c r="BD2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="BC2" s="11" t="s">
+      <c r="BE2" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="BD2" s="11" t="s">
+      <c r="BF2" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="BE2" s="11" t="s">
+      <c r="BG2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="BF2" s="11" t="s">
+      <c r="BH2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BI2" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BJ2" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="BI2" s="11" t="s">
+      <c r="BK2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="BJ2" s="11" t="s">
+      <c r="BL2" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="BK2" s="11" t="s">
+      <c r="BM2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="BL2" s="11" t="s">
+      <c r="BN2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="BM2" s="11" t="s">
+      <c r="BO2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="BN2" s="11" t="s">
+      <c r="BP2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BO2" s="11" t="s">
+      <c r="BQ2" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="BP2" s="11" t="s">
+      <c r="BR2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="BQ2" s="11" t="s">
+      <c r="BS2" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="BR2" s="11" t="s">
+      <c r="BT2" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:70" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:72" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>120</v>
       </c>
@@ -1546,145 +1578,151 @@
         <v>194</v>
       </c>
       <c r="Y3" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z3" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AD3" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AE3" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AF3" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AG3" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AH3" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AI3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AJ3" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AK3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="AJ3" s="7" t="s">
+      <c r="AL3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AM3" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AN3" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AO3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AP3" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AQ3" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AR3" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="AS3" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="AT3" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AU3" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="AV3" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="AW3" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="AX3" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="AY3" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="AZ3" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="BA3" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="BB3" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="BA3" s="7" t="s">
+      <c r="BC3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="BB3" s="7" t="s">
+      <c r="BD3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="BC3" s="7" t="s">
+      <c r="BE3" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="BD3" s="7" t="s">
+      <c r="BF3" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="BE3" s="7" t="s">
+      <c r="BG3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="BF3" s="7" t="s">
+      <c r="BH3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="BG3" s="7" t="s">
+      <c r="BI3" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="BH3" s="7" t="s">
+      <c r="BJ3" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="BI3" s="7" t="s">
+      <c r="BK3" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="BJ3" s="7" t="s">
+      <c r="BL3" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="BK3" s="7" t="s">
+      <c r="BM3" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="BL3" s="7" t="s">
+      <c r="BN3" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="BM3" s="7" t="s">
+      <c r="BO3" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="BN3" s="7" t="s">
+      <c r="BP3" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="BO3" s="7" t="s">
+      <c r="BQ3" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="BP3" s="7" t="s">
+      <c r="BR3" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="BQ3" s="7" t="s">
+      <c r="BS3" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="BR3" s="7" t="s">
+      <c r="BT3" s="7" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:70" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:72" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>112</v>
       </c>
@@ -1758,152 +1796,158 @@
         <v>195</v>
       </c>
       <c r="Y4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z4" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AA4" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB4" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="AA4" s="9" t="s">
+      <c r="AC4" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AD4" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="AC4" s="9" t="s">
+      <c r="AE4" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="AD4" s="9" t="s">
+      <c r="AF4" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="AE4" s="9" t="s">
+      <c r="AG4" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="AF4" s="9" t="s">
+      <c r="AH4" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="AG4" s="9" t="s">
+      <c r="AI4" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="AH4" s="9" t="s">
+      <c r="AJ4" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="AI4" s="9" t="s">
+      <c r="AK4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AJ4" s="9" t="s">
+      <c r="AL4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AK4" s="9" t="s">
+      <c r="AM4" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="AL4" s="9" t="s">
+      <c r="AN4" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="AM4" s="9" t="s">
+      <c r="AO4" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="AN4" s="9" t="s">
+      <c r="AP4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AO4" s="9" t="s">
+      <c r="AQ4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AP4" s="9" t="s">
+      <c r="AR4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="AQ4" s="9" t="s">
+      <c r="AS4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="AR4" s="9" t="s">
+      <c r="AT4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="AS4" s="9" t="s">
+      <c r="AU4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AT4" s="9" t="s">
+      <c r="AV4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="AU4" s="9" t="s">
+      <c r="AW4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AV4" s="9" t="s">
+      <c r="AX4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AW4" s="9" t="s">
+      <c r="AY4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AX4" s="9" t="s">
+      <c r="AZ4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AY4" s="9" t="s">
+      <c r="BA4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AZ4" s="9" t="s">
+      <c r="BB4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BA4" s="9" t="s">
+      <c r="BC4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BB4" s="9" t="s">
+      <c r="BD4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BC4" s="9" t="s">
+      <c r="BE4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BD4" s="9" t="s">
+      <c r="BF4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="BE4" s="9" t="s">
+      <c r="BG4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="BF4" s="9" t="s">
+      <c r="BH4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="BG4" s="9" t="s">
+      <c r="BI4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="BH4" s="9" t="s">
+      <c r="BJ4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="BI4" s="9" t="s">
+      <c r="BK4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="BJ4" s="9" t="s">
+      <c r="BL4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BK4" s="9" t="s">
+      <c r="BM4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="BL4" s="9" t="s">
+      <c r="BN4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="BM4" s="9" t="s">
+      <c r="BO4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="BN4" s="9" t="s">
+      <c r="BP4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="BO4" s="9" t="s">
+      <c r="BQ4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="BP4" s="9" t="s">
+      <c r="BR4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="BQ4" s="9" t="s">
+      <c r="BS4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="BR4" s="10" t="s">
+      <c r="BT4" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BR4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BT4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
@@ -1,36 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\jy_aps\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A83DD0-294F-4B0E-8B32-B0F8ACD9DD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BU$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BW$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t>{factoryName}</t>
   </si>
@@ -699,21 +692,38 @@
   </si>
   <si>
     <t>{.totalAll}</t>
+  </si>
+  <si>
+    <t>{.lastMonthOverdueQtyA}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastMonthOverdueQty}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastMonthOverdueQty}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastMonthValidFlag}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastMonthValidFlag}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0;\-0;;@"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -725,6 +735,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -733,6 +744,7 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -740,6 +752,7 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -747,6 +760,7 @@
       <b/>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -755,162 +769,52 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -935,194 +839,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1145,255 +863,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1430,62 +906,31 @@
     <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1743,39 +1188,40 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:BU7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BX7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="3" width="7.91666666666667" customWidth="1"/>
-    <col min="4" max="4" width="33.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="12.1666666666667" customWidth="1"/>
-    <col min="6" max="7" width="9.33333333333333" customWidth="1"/>
-    <col min="8" max="8" width="8.83333333333333" customWidth="1"/>
+    <col min="2" max="3" width="7.9140625" customWidth="1"/>
+    <col min="4" max="4" width="33.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="6" max="7" width="9.33203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
     <col min="9" max="9" width="30.5" customWidth="1"/>
-    <col min="10" max="10" width="5.16666666666667" customWidth="1"/>
-    <col min="11" max="12" width="9.83333333333333" customWidth="1"/>
-    <col min="13" max="15" width="9.08333333333333" customWidth="1"/>
-    <col min="16" max="16" width="4.58333333333333" customWidth="1"/>
-    <col min="17" max="17" width="7.83333333333333" customWidth="1"/>
-    <col min="18" max="19" width="5.41666666666667" customWidth="1"/>
-    <col min="20" max="20" width="5.91666666666667" customWidth="1"/>
+    <col min="10" max="10" width="5.1640625" customWidth="1"/>
+    <col min="11" max="12" width="9.83203125" customWidth="1"/>
+    <col min="13" max="15" width="9.08203125" customWidth="1"/>
+    <col min="16" max="16" width="4.58203125" customWidth="1"/>
+    <col min="17" max="17" width="7.83203125" customWidth="1"/>
+    <col min="18" max="19" width="5.4140625" customWidth="1"/>
+    <col min="20" max="20" width="5.9140625" customWidth="1"/>
     <col min="21" max="22" width="5.75" customWidth="1"/>
-    <col min="23" max="29" width="6.33333333333333" customWidth="1"/>
-    <col min="30" max="37" width="7.08333333333333" customWidth="1"/>
-    <col min="38" max="72" width="6.08333333333333" customWidth="1"/>
-    <col min="73" max="73" width="8.41666666666667" customWidth="1"/>
-    <col min="74" max="77" width="6.08333333333333" customWidth="1"/>
-    <col min="78" max="79" width="16.75" customWidth="1"/>
+    <col min="23" max="31" width="6.33203125" customWidth="1"/>
+    <col min="32" max="39" width="7.08203125" customWidth="1"/>
+    <col min="40" max="74" width="6.08203125" customWidth="1"/>
+    <col min="75" max="75" width="8.4140625" customWidth="1"/>
+    <col min="76" max="76" width="6.08203125" hidden="1" customWidth="1"/>
+    <col min="77" max="79" width="6.08203125" customWidth="1"/>
+    <col min="80" max="81" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30.75" customHeight="1" spans="1:73">
+    <row r="1" spans="1:76" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1817,11 +1263,11 @@
       <c r="AK1" s="5"/>
       <c r="AL1" s="5"/>
       <c r="AM1" s="5"/>
-      <c r="AN1" s="5" t="s">
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
       <c r="AQ1" s="5"/>
       <c r="AR1" s="5"/>
       <c r="AS1" s="5"/>
@@ -1844,21 +1290,23 @@
       <c r="BJ1" s="5"/>
       <c r="BK1" s="5"/>
       <c r="BL1" s="5"/>
-      <c r="BM1" s="5" t="s">
+      <c r="BM1" s="5"/>
+      <c r="BN1" s="5"/>
+      <c r="BO1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="BN1" s="5"/>
-      <c r="BO1" s="5"/>
       <c r="BP1" s="5"/>
       <c r="BQ1" s="5"/>
-      <c r="BR1" s="5" t="s">
+      <c r="BR1" s="5"/>
+      <c r="BS1" s="5"/>
+      <c r="BT1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="BS1" s="5"/>
-      <c r="BT1" s="5"/>
       <c r="BU1" s="5"/>
+      <c r="BV1" s="5"/>
+      <c r="BW1" s="5"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="11.5" customHeight="1" spans="1:73">
+    <row r="2" spans="1:76" s="1" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -1943,143 +1391,147 @@
       <c r="AB2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AF2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AG2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AH2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AG2" s="10" t="s">
+      <c r="AI2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH2" s="10" t="s">
+      <c r="AJ2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AK2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AL2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AM2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AN2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AO2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="AN2" s="10" t="s">
+      <c r="AP2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AO2" s="10" t="s">
+      <c r="AQ2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AR2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AQ2" s="10" t="s">
+      <c r="AS2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AT2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AS2" s="10" t="s">
+      <c r="AU2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AV2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AW2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV2" s="10" t="s">
+      <c r="AX2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="AY2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AX2" s="10" t="s">
+      <c r="AZ2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AY2" s="10" t="s">
+      <c r="BA2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="AZ2" s="10" t="s">
+      <c r="BB2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="BA2" s="10" t="s">
+      <c r="BC2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="BB2" s="10" t="s">
+      <c r="BD2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="BC2" s="10" t="s">
+      <c r="BE2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="BD2" s="10" t="s">
+      <c r="BF2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="BE2" s="10" t="s">
+      <c r="BG2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="BF2" s="10" t="s">
+      <c r="BH2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="BG2" s="10" t="s">
+      <c r="BI2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="BH2" s="10" t="s">
+      <c r="BJ2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="BI2" s="10" t="s">
+      <c r="BK2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="BJ2" s="10" t="s">
+      <c r="BL2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="BK2" s="10" t="s">
+      <c r="BM2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BN2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="BM2" s="10" t="s">
+      <c r="BO2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="BN2" s="10" t="s">
+      <c r="BP2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="BO2" s="10" t="s">
+      <c r="BQ2" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="BP2" s="10" t="s">
+      <c r="BR2" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="BQ2" s="10" t="s">
+      <c r="BS2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="BR2" s="10" t="s">
+      <c r="BT2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="BS2" s="10" t="s">
+      <c r="BU2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="BT2" s="10" t="s">
+      <c r="BV2" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="BU2" s="10" t="s">
+      <c r="BW2" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="48" customHeight="1" spans="1:73">
+    <row r="3" spans="1:76" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>77</v>
       </c>
@@ -2164,143 +1616,149 @@
       <c r="AB3" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AC3" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="AE3" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AF3" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AG3" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AH3" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AI3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AJ3" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AK3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AJ3" s="7" t="s">
+      <c r="AL3" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AM3" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AN3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AO3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AP3" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AQ3" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AR3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="AS3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="AT3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AU3" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="AV3" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="AW3" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="AX3" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="AY3" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="AZ3" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="BA3" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="BB3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="BA3" s="7" t="s">
+      <c r="BC3" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="BB3" s="7" t="s">
+      <c r="BD3" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="BC3" s="7" t="s">
+      <c r="BE3" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="BD3" s="7" t="s">
+      <c r="BF3" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="BE3" s="7" t="s">
+      <c r="BG3" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="BF3" s="7" t="s">
+      <c r="BH3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="BG3" s="7" t="s">
+      <c r="BI3" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="BH3" s="7" t="s">
+      <c r="BJ3" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="BI3" s="7" t="s">
+      <c r="BK3" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="BJ3" s="7" t="s">
+      <c r="BL3" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="BK3" s="7" t="s">
+      <c r="BM3" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="BL3" s="7" t="s">
+      <c r="BN3" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="BM3" s="7" t="s">
+      <c r="BO3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="BN3" s="7" t="s">
+      <c r="BP3" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="BO3" s="7" t="s">
+      <c r="BQ3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="BP3" s="7" t="s">
+      <c r="BR3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="BQ3" s="7" t="s">
+      <c r="BS3" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="BR3" s="7" t="s">
+      <c r="BT3" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="BS3" s="7" t="s">
+      <c r="BU3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="BT3" s="7" t="s">
+      <c r="BV3" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="BU3" s="7" t="s">
+      <c r="BW3" s="7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="14.5" customHeight="1" spans="1:73">
+    <row r="4" spans="1:76" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>150</v>
       </c>
@@ -2385,154 +1843,162 @@
       <c r="AB4" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="AC4" s="8" t="s">
+      <c r="AC4" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD4" s="18" t="str">
+        <f>IF(ISBLANK(B4),"",IF(AL4=SUM(AR4:BV4),BX4,"否"))</f>
+        <v>否</v>
+      </c>
+      <c r="AE4" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="AD4" s="8" t="s">
+      <c r="AF4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AE4" s="8" t="s">
+      <c r="AG4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="AF4" s="8" t="s">
+      <c r="AH4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="AG4" s="8" t="s">
+      <c r="AI4" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="AH4" s="8" t="s">
+      <c r="AJ4" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="AI4" s="8" t="s">
+      <c r="AK4" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="AJ4" s="8" t="s">
+      <c r="AL4" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="AK4" s="8" t="s">
+      <c r="AM4" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AL4" s="8" t="s">
+      <c r="AN4" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="AM4" s="8" t="s">
+      <c r="AO4" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="AN4" s="8" t="s">
+      <c r="AP4" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="AO4" s="8" t="s">
+      <c r="AQ4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="AP4" s="8" t="s">
+      <c r="AR4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="AQ4" s="8" t="s">
+      <c r="AS4" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="AR4" s="8" t="s">
+      <c r="AT4" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="AS4" s="8" t="s">
+      <c r="AU4" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="AT4" s="8" t="s">
+      <c r="AV4" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="AU4" s="8" t="s">
+      <c r="AW4" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="AV4" s="8" t="s">
+      <c r="AX4" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="AW4" s="8" t="s">
+      <c r="AY4" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="AX4" s="8" t="s">
+      <c r="AZ4" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="AY4" s="8" t="s">
+      <c r="BA4" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="AZ4" s="8" t="s">
+      <c r="BB4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="BA4" s="8" t="s">
+      <c r="BC4" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="BB4" s="8" t="s">
+      <c r="BD4" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="BC4" s="8" t="s">
+      <c r="BE4" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="BD4" s="8" t="s">
+      <c r="BF4" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="BE4" s="8" t="s">
+      <c r="BG4" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="BF4" s="8" t="s">
+      <c r="BH4" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="BG4" s="8" t="s">
+      <c r="BI4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="BH4" s="8" t="s">
+      <c r="BJ4" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="BI4" s="8" t="s">
+      <c r="BK4" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="BJ4" s="8" t="s">
+      <c r="BL4" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="BK4" s="8" t="s">
+      <c r="BM4" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="BL4" s="8" t="s">
+      <c r="BN4" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="BM4" s="8" t="s">
+      <c r="BO4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="BN4" s="8" t="s">
+      <c r="BP4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="BO4" s="8" t="s">
+      <c r="BQ4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="BP4" s="8" t="s">
+      <c r="BR4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="BQ4" s="8" t="s">
+      <c r="BS4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="BR4" s="8" t="s">
+      <c r="BT4" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="BS4" s="8" t="s">
+      <c r="BU4" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="BT4" s="8" t="s">
+      <c r="BV4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="BU4" s="13" t="s">
+      <c r="BW4" s="13" t="s">
         <v>222</v>
       </c>
+      <c r="BX4" s="17" t="s">
+        <v>227</v>
+      </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:BU4" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A4:BW4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldFinalResultExportTemp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\jy_aps\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A83DD0-294F-4B0E-8B32-B0F8ACD9DD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D881E6A7-326A-4B53-BFC1-D0A339AA89AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BW$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$CE$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
   <si>
     <t>{factoryName}</t>
   </si>
@@ -712,6 +712,84 @@
   <si>
     <t>{.lastMonthValidFlag}</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay10A}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay9A}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay8A}</t>
+  </si>
+  <si>
+    <t>{.lastDay7A}</t>
+  </si>
+  <si>
+    <t>{.lastDay6A}</t>
+  </si>
+  <si>
+    <t>{.lastDay5A}</t>
+  </si>
+  <si>
+    <t>{.lastDay4A}</t>
+  </si>
+  <si>
+    <t>{.lastDay3A}</t>
+  </si>
+  <si>
+    <t>{lastDay10}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDay9}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDay8}</t>
+  </si>
+  <si>
+    <t>{lastDay7}</t>
+  </si>
+  <si>
+    <t>{lastDay6}</t>
+  </si>
+  <si>
+    <t>{lastDay5}</t>
+  </si>
+  <si>
+    <t>{lastDay4}</t>
+  </si>
+  <si>
+    <t>{lastDay3}</t>
+  </si>
+  <si>
+    <t>{.lastDay10}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay9}</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay8}</t>
+  </si>
+  <si>
+    <t>{.lastDay7}</t>
+  </si>
+  <si>
+    <t>{.lastDay6}</t>
+  </si>
+  <si>
+    <t>{.lastDay5}</t>
+  </si>
+  <si>
+    <t>{.lastDay4}</t>
+  </si>
+  <si>
+    <t>{.lastDay3}</t>
   </si>
 </sst>
 </file>
@@ -814,7 +892,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -837,6 +915,11 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
       </patternFill>
     </fill>
   </fills>
@@ -869,7 +952,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -919,6 +1002,7 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1194,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BX7"/>
+  <dimension ref="A1:CF7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1214,14 +1298,14 @@
     <col min="21" max="22" width="5.75" customWidth="1"/>
     <col min="23" max="31" width="6.33203125" customWidth="1"/>
     <col min="32" max="39" width="7.08203125" customWidth="1"/>
-    <col min="40" max="74" width="6.08203125" customWidth="1"/>
-    <col min="75" max="75" width="8.4140625" customWidth="1"/>
-    <col min="76" max="76" width="6.08203125" hidden="1" customWidth="1"/>
-    <col min="77" max="79" width="6.08203125" customWidth="1"/>
-    <col min="80" max="81" width="16.75" customWidth="1"/>
+    <col min="40" max="82" width="6.08203125" customWidth="1"/>
+    <col min="83" max="83" width="8.4140625" customWidth="1"/>
+    <col min="84" max="84" width="6.08203125" hidden="1" customWidth="1"/>
+    <col min="85" max="87" width="6.08203125" customWidth="1"/>
+    <col min="88" max="89" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:84" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1265,9 +1349,7 @@
       <c r="AM1" s="5"/>
       <c r="AN1" s="5"/>
       <c r="AO1" s="5"/>
-      <c r="AP1" s="5" t="s">
-        <v>1</v>
-      </c>
+      <c r="AP1" s="5"/>
       <c r="AQ1" s="5"/>
       <c r="AR1" s="5"/>
       <c r="AS1" s="5"/>
@@ -1275,7 +1357,9 @@
       <c r="AU1" s="5"/>
       <c r="AV1" s="5"/>
       <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
+      <c r="AX1" s="5" t="s">
+        <v>1</v>
+      </c>
       <c r="AY1" s="5"/>
       <c r="AZ1" s="5"/>
       <c r="BA1" s="5"/>
@@ -1292,21 +1376,29 @@
       <c r="BL1" s="5"/>
       <c r="BM1" s="5"/>
       <c r="BN1" s="5"/>
-      <c r="BO1" s="5" t="s">
-        <v>2</v>
-      </c>
+      <c r="BO1" s="5"/>
       <c r="BP1" s="5"/>
       <c r="BQ1" s="5"/>
       <c r="BR1" s="5"/>
       <c r="BS1" s="5"/>
-      <c r="BT1" s="5" t="s">
-        <v>3</v>
-      </c>
+      <c r="BT1" s="5"/>
       <c r="BU1" s="5"/>
       <c r="BV1" s="5"/>
-      <c r="BW1" s="5"/>
+      <c r="BW1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="BX1" s="5"/>
+      <c r="BY1" s="5"/>
+      <c r="BZ1" s="5"/>
+      <c r="CA1" s="5"/>
+      <c r="CB1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="CC1" s="5"/>
+      <c r="CD1" s="5"/>
+      <c r="CE1" s="5"/>
     </row>
-    <row r="2" spans="1:76" s="1" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:84" s="1" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -1428,110 +1520,134 @@
       <c r="AO2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AP2" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AQ2" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="AR2" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AS2" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT2" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AU2" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="AV2" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="AW2" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="AX2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AQ2" s="10" t="s">
+      <c r="AY2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AZ2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AS2" s="10" t="s">
+      <c r="BA2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="BB2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="BC2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AV2" s="10" t="s">
+      <c r="BD2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="BE2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AX2" s="10" t="s">
+      <c r="BF2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AY2" s="10" t="s">
+      <c r="BG2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="AZ2" s="10" t="s">
+      <c r="BH2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="BA2" s="10" t="s">
+      <c r="BI2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="BB2" s="10" t="s">
+      <c r="BJ2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="BC2" s="10" t="s">
+      <c r="BK2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="BD2" s="10" t="s">
+      <c r="BL2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="BE2" s="10" t="s">
+      <c r="BM2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="BF2" s="10" t="s">
+      <c r="BN2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="BG2" s="10" t="s">
+      <c r="BO2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="BH2" s="10" t="s">
+      <c r="BP2" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="BI2" s="10" t="s">
+      <c r="BQ2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="BJ2" s="10" t="s">
+      <c r="BR2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="BK2" s="10" t="s">
+      <c r="BS2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BT2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="BM2" s="10" t="s">
+      <c r="BU2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="BN2" s="10" t="s">
+      <c r="BV2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="BO2" s="10" t="s">
+      <c r="BW2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="BP2" s="10" t="s">
+      <c r="BX2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="BQ2" s="10" t="s">
+      <c r="BY2" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="BR2" s="10" t="s">
+      <c r="BZ2" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="BS2" s="10" t="s">
+      <c r="CA2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="BT2" s="10" t="s">
+      <c r="CB2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="BU2" s="10" t="s">
+      <c r="CC2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="BV2" s="10" t="s">
+      <c r="CD2" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="BW2" s="10" t="s">
+      <c r="CE2" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:76" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:84" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>77</v>
       </c>
@@ -1656,109 +1772,133 @@
         <v>115</v>
       </c>
       <c r="AP3" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS3" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="AT3" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="AU3" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="AV3" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="AW3" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="AX3" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="AY3" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="AZ3" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="BA3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="BB3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="BC3" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="BD3" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="BE3" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="BF3" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="BG3" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="BH3" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="BA3" s="7" t="s">
+      <c r="BI3" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="BB3" s="7" t="s">
+      <c r="BJ3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="BC3" s="7" t="s">
+      <c r="BK3" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="BD3" s="7" t="s">
+      <c r="BL3" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="BE3" s="7" t="s">
+      <c r="BM3" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="BF3" s="7" t="s">
+      <c r="BN3" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="BG3" s="7" t="s">
+      <c r="BO3" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="BH3" s="7" t="s">
+      <c r="BP3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="BI3" s="7" t="s">
+      <c r="BQ3" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="BJ3" s="7" t="s">
+      <c r="BR3" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="BK3" s="7" t="s">
+      <c r="BS3" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="BL3" s="7" t="s">
+      <c r="BT3" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="BM3" s="7" t="s">
+      <c r="BU3" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="BN3" s="7" t="s">
+      <c r="BV3" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="BO3" s="7" t="s">
+      <c r="BW3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="BP3" s="7" t="s">
+      <c r="BX3" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="BQ3" s="7" t="s">
+      <c r="BY3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="BR3" s="7" t="s">
+      <c r="BZ3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="BS3" s="7" t="s">
+      <c r="CA3" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="BT3" s="7" t="s">
+      <c r="CB3" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="BU3" s="7" t="s">
+      <c r="CC3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="BV3" s="7" t="s">
+      <c r="CD3" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="BW3" s="7" t="s">
+      <c r="CE3" s="7" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="1:76" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:84" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>150</v>
       </c>
@@ -1847,7 +1987,7 @@
         <v>225</v>
       </c>
       <c r="AD4" s="18" t="str">
-        <f>IF(ISBLANK(B4),"",IF(AL4=SUM(AR4:BV4),BX4,"否"))</f>
+        <f>IF(ISBLANK(B4),"",IF(AL4=SUM(AZ4:CD4),CF4,"否"))</f>
         <v>否</v>
       </c>
       <c r="AE4" s="8" t="s">
@@ -1884,121 +2024,145 @@
         <v>188</v>
       </c>
       <c r="AP4" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="AQ4" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="AR4" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="AS4" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="AT4" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="AU4" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="AV4" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="AW4" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="AX4" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="AQ4" s="8" t="s">
+      <c r="AY4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="AR4" s="8" t="s">
+      <c r="AZ4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="AS4" s="8" t="s">
+      <c r="BA4" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="AT4" s="8" t="s">
+      <c r="BB4" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="AU4" s="8" t="s">
+      <c r="BC4" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="AV4" s="8" t="s">
+      <c r="BD4" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="AW4" s="8" t="s">
+      <c r="BE4" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="AX4" s="8" t="s">
+      <c r="BF4" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="AY4" s="8" t="s">
+      <c r="BG4" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="AZ4" s="8" t="s">
+      <c r="BH4" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="BA4" s="8" t="s">
+      <c r="BI4" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="BB4" s="8" t="s">
+      <c r="BJ4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="BC4" s="8" t="s">
+      <c r="BK4" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="BD4" s="8" t="s">
+      <c r="BL4" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="BE4" s="8" t="s">
+      <c r="BM4" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="BF4" s="8" t="s">
+      <c r="BN4" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="BG4" s="8" t="s">
+      <c r="BO4" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="BH4" s="8" t="s">
+      <c r="BP4" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="BI4" s="8" t="s">
+      <c r="BQ4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="BJ4" s="8" t="s">
+      <c r="BR4" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="BK4" s="8" t="s">
+      <c r="BS4" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="BL4" s="8" t="s">
+      <c r="BT4" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="BM4" s="8" t="s">
+      <c r="BU4" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="BN4" s="8" t="s">
+      <c r="BV4" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="BO4" s="8" t="s">
+      <c r="BW4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="BP4" s="8" t="s">
+      <c r="BX4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="BQ4" s="8" t="s">
+      <c r="BY4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="BR4" s="8" t="s">
+      <c r="BZ4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="BS4" s="8" t="s">
+      <c r="CA4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="BT4" s="8" t="s">
+      <c r="CB4" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="BU4" s="8" t="s">
+      <c r="CC4" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="BV4" s="8" t="s">
+      <c r="CD4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="BW4" s="13" t="s">
+      <c r="CE4" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="BX4" s="17" t="s">
+      <c r="CF4" s="17" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:76" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BW4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:CE4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>